--- a/03_Outputs/Agroindustrial_Occidente/09_Salud/salud.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/09_Salud/salud.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="E8" s="5">
-        <v>0.0942289561724751</v>
+        <v>0.0942289561724752</v>
       </c>
     </row>
     <row r="9">
@@ -958,7 +958,7 @@
         <v>71.7681037517152</v>
       </c>
       <c r="F8" s="9">
-        <v>888.912270502074</v>
+        <v>888.912270502075</v>
       </c>
       <c r="G8" s="11">
         <v>49.3097888820581</v>
